--- a/data/trans_orig/P79A8_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A8_2023-Estudios-trans_orig.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -743,17 +743,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -778,17 +778,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
